--- a/fixtures/saxo-nl/Transactions_10000000_2024-01-01_2024-12-31.xlsx
+++ b/fixtures/saxo-nl/Transactions_10000000_2024-01-01_2024-12-31.xlsx
@@ -8,13 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="Transacties" sheetId="1" r:id="rId1"/>
+    <sheet name="_Transacties" sheetId="2" r:id="rId2"/>
+    <sheet name="Bookings" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="218">
   <si>
     <t>Klant-id</t>
   </si>
@@ -151,7 +153,7 @@
     <t>40100/9000001EUR</t>
   </si>
   <si>
-    <t>40000000884</t>
+    <t>40000002522</t>
   </si>
   <si>
     <t>Geldoverboeking</t>
@@ -166,13 +168,13 @@
     <t>Cash</t>
   </si>
   <si>
-    <t>40000000871</t>
+    <t>40000002509</t>
   </si>
   <si>
     <t>Saxo Service Fee - October 2024</t>
   </si>
   <si>
-    <t>40000000858</t>
+    <t>40000002496</t>
   </si>
   <si>
     <t>Saxo Service Fee - September 2024</t>
@@ -202,7 +204,7 @@
     <t>5000189</t>
   </si>
   <si>
-    <t>40000000845</t>
+    <t>40000002431</t>
   </si>
   <si>
     <t>Saxo Service Fee - August 2024</t>
@@ -226,7 +228,7 @@
     <t>Euronext Amsterdam</t>
   </si>
   <si>
-    <t>40000000832</t>
+    <t>40000002392</t>
   </si>
   <si>
     <t>Rente</t>
@@ -247,13 +249,13 @@
     <t>XF0000000087</t>
   </si>
   <si>
-    <t>40000000819</t>
+    <t>40000002353</t>
   </si>
   <si>
     <t>Saxo Service Fee - July 2024</t>
   </si>
   <si>
-    <t>40000000806</t>
+    <t>40000002340</t>
   </si>
   <si>
     <t>Saxo Service Fee - May 2024</t>
@@ -262,7 +264,7 @@
     <t>5000186</t>
   </si>
   <si>
-    <t>40000000793</t>
+    <t>40000002301</t>
   </si>
   <si>
     <t>Saxo Service Fee - June 2024</t>
@@ -289,7 +291,7 @@
     <t>Euronext Amsterdam Funds</t>
   </si>
   <si>
-    <t>40000000780</t>
+    <t>40000002236</t>
   </si>
   <si>
     <t>5000171</t>
@@ -310,13 +312,13 @@
     <t>5000162</t>
   </si>
   <si>
-    <t>40000000767</t>
+    <t>40000002184</t>
   </si>
   <si>
     <t>Saxo Service Fee Green - April 2024</t>
   </si>
   <si>
-    <t>40000000754</t>
+    <t>40000002171</t>
   </si>
   <si>
     <t>Client Interest - Apr 2024</t>
@@ -325,7 +327,7 @@
     <t>5000174</t>
   </si>
   <si>
-    <t>40000000741</t>
+    <t>40000002158</t>
   </si>
   <si>
     <t>ADR-kosten</t>
@@ -346,13 +348,13 @@
     <t>NASDAQ (Small cap)</t>
   </si>
   <si>
-    <t>40000000728</t>
+    <t>40000002093</t>
   </si>
   <si>
     <t>Saxo Service Fee Green - March 2024</t>
   </si>
   <si>
-    <t>40000000715</t>
+    <t>40000002080</t>
   </si>
   <si>
     <t>Client Interest - Mar 2024</t>
@@ -364,51 +366,319 @@
     <t>5000168</t>
   </si>
   <si>
-    <t>40000000689</t>
+    <t>40000002028</t>
   </si>
   <si>
     <t>Client Interest - Feb 2024</t>
   </si>
   <si>
-    <t>40000000702</t>
+    <t>40000002041</t>
   </si>
   <si>
     <t>Saxo Service Fee Green - February 2024</t>
   </si>
   <si>
-    <t>40000000663</t>
+    <t>40000002002</t>
   </si>
   <si>
     <t>Client Interest - Jan 2024</t>
   </si>
   <si>
-    <t>40000000676</t>
+    <t>40000002015</t>
   </si>
   <si>
     <t>Saxo Service Fee Green - January 2024</t>
   </si>
   <si>
-    <t>40000000637</t>
+    <t>40000001950</t>
   </si>
   <si>
     <t>Client Interest - Dec 2023</t>
   </si>
   <si>
-    <t>40000000650</t>
+    <t>40000001963</t>
   </si>
   <si>
     <t>Saxo Service Fee Green - December 2023</t>
   </si>
   <si>
     <t>5000156</t>
+  </si>
+  <si>
+    <t>Order-ID</t>
+  </si>
+  <si>
+    <t>Aangepaste transactiedatum</t>
+  </si>
+  <si>
+    <t>Uitvoeringsdatum transactie</t>
+  </si>
+  <si>
+    <t>Trade Event Type</t>
+  </si>
+  <si>
+    <t>Trade Type</t>
+  </si>
+  <si>
+    <t>Openen/sluiten</t>
+  </si>
+  <si>
+    <t>Traded Quantity</t>
+  </si>
+  <si>
+    <t>Prijs</t>
+  </si>
+  <si>
+    <t>Verhandelde waarde</t>
+  </si>
+  <si>
+    <t>Spreadkosten</t>
+  </si>
+  <si>
+    <t>7000000203</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Gekocht</t>
+  </si>
+  <si>
+    <t>NotAvailable</t>
+  </si>
+  <si>
+    <t>Te openen</t>
+  </si>
+  <si>
+    <t>Amount Type</t>
+  </si>
+  <si>
+    <t>Amount Type Id</t>
+  </si>
+  <si>
+    <t>Boekingsdatum</t>
+  </si>
+  <si>
+    <t>Ex-datum</t>
+  </si>
+  <si>
+    <t>Boekdatum</t>
+  </si>
+  <si>
+    <t>In aanmerking komend aantal</t>
+  </si>
+  <si>
+    <t>Dividend per aandeel</t>
+  </si>
+  <si>
+    <t>Tax Percentage</t>
+  </si>
+  <si>
+    <t>40000002535</t>
+  </si>
+  <si>
+    <t>Corporate Actions - Cashdividenden</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>21-nov-2024</t>
+  </si>
+  <si>
+    <t>17-sep-2024</t>
+  </si>
+  <si>
+    <t>0.89 USD</t>
+  </si>
+  <si>
+    <t>40000002548</t>
+  </si>
+  <si>
+    <t>Corporate actions - Voorheffing</t>
+  </si>
+  <si>
+    <t>55</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>477</t>
+  </si>
+  <si>
+    <t>40000002470</t>
+  </si>
+  <si>
+    <t>30-aug-2024</t>
+  </si>
+  <si>
+    <t>0.07 CAD</t>
+  </si>
+  <si>
+    <t>40000002483</t>
+  </si>
+  <si>
+    <t>40000002457</t>
+  </si>
+  <si>
+    <t>15-aug-2024</t>
+  </si>
+  <si>
+    <t>13-jun-2024</t>
+  </si>
+  <si>
+    <t>40000002444</t>
+  </si>
+  <si>
+    <t>0.74 USD</t>
+  </si>
+  <si>
+    <t>40000002418</t>
+  </si>
+  <si>
+    <t>Corporate actions - Fracties</t>
+  </si>
+  <si>
+    <t>57</t>
+  </si>
+  <si>
+    <t>05-aug-2024</t>
+  </si>
+  <si>
+    <t>01-feb-2024</t>
+  </si>
+  <si>
+    <t>40000002405</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t>40000002366</t>
+  </si>
+  <si>
+    <t>26-jul-2024</t>
+  </si>
+  <si>
+    <t>24-jul-2024</t>
+  </si>
+  <si>
+    <t>40000002379</t>
+  </si>
+  <si>
+    <t>40000002314</t>
+  </si>
+  <si>
+    <t>31-mei-2024</t>
+  </si>
+  <si>
+    <t>29-apr-2024</t>
+  </si>
+  <si>
+    <t>40000002327</t>
+  </si>
+  <si>
+    <t>40000002288</t>
+  </si>
+  <si>
+    <t>15-mei-2024</t>
+  </si>
+  <si>
+    <t>13-mrt-2024</t>
+  </si>
+  <si>
+    <t>40000002275</t>
+  </si>
+  <si>
+    <t>40000002262</t>
+  </si>
+  <si>
+    <t>30-mei-2024</t>
+  </si>
+  <si>
+    <t>26-apr-2024</t>
+  </si>
+  <si>
+    <t>40000002249</t>
+  </si>
+  <si>
+    <t>1.96 EUR</t>
+  </si>
+  <si>
+    <t>40000002223</t>
+  </si>
+  <si>
+    <t>09-mei-2024</t>
+  </si>
+  <si>
+    <t>40000002197</t>
+  </si>
+  <si>
+    <t>24-apr-2024</t>
+  </si>
+  <si>
+    <t>03-nov-2023</t>
+  </si>
+  <si>
+    <t>40000002210</t>
+  </si>
+  <si>
+    <t>40000002132</t>
+  </si>
+  <si>
+    <t>19-apr-2024</t>
+  </si>
+  <si>
+    <t>31-jan-2024</t>
+  </si>
+  <si>
+    <t>40000002145</t>
+  </si>
+  <si>
+    <t>1000002</t>
+  </si>
+  <si>
+    <t>40000002119</t>
+  </si>
+  <si>
+    <t>29-feb-2024</t>
+  </si>
+  <si>
+    <t>21-nov-2023</t>
+  </si>
+  <si>
+    <t>40000002106</t>
+  </si>
+  <si>
+    <t>40000002067</t>
+  </si>
+  <si>
+    <t>14-feb-2024</t>
+  </si>
+  <si>
+    <t>30-nov-2023</t>
+  </si>
+  <si>
+    <t>40000002054</t>
+  </si>
+  <si>
+    <t>40000001976</t>
+  </si>
+  <si>
+    <t>30-okt-2023</t>
+  </si>
+  <si>
+    <t>40000001989</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy hh:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -439,9 +709,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3049,4 +3320,2746 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:X2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:24">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H1" t="s">
+        <v>130</v>
+      </c>
+      <c r="I1" t="s">
+        <v>131</v>
+      </c>
+      <c r="J1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K1" t="s">
+        <v>133</v>
+      </c>
+      <c r="L1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M1" t="s">
+        <v>135</v>
+      </c>
+      <c r="N1" t="s">
+        <v>136</v>
+      </c>
+      <c r="O1" t="s">
+        <v>137</v>
+      </c>
+      <c r="P1" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S1" t="s">
+        <v>23</v>
+      </c>
+      <c r="T1" t="s">
+        <v>24</v>
+      </c>
+      <c r="U1" t="s">
+        <v>25</v>
+      </c>
+      <c r="V1" t="s">
+        <v>26</v>
+      </c>
+      <c r="W1" t="s">
+        <v>27</v>
+      </c>
+      <c r="X1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H2" s="1">
+        <v>45428</v>
+      </c>
+      <c r="I2" s="2">
+        <v>45428.4716550926</v>
+      </c>
+      <c r="J2" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" t="s">
+        <v>142</v>
+      </c>
+      <c r="L2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>34</v>
+      </c>
+      <c r="O2">
+        <v>-34</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T2" t="s">
+        <v>94</v>
+      </c>
+      <c r="U2" t="s">
+        <v>95</v>
+      </c>
+      <c r="V2" t="s">
+        <v>36</v>
+      </c>
+      <c r="W2" t="s">
+        <v>41</v>
+      </c>
+      <c r="X2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:U48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:21">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" t="s">
+        <v>144</v>
+      </c>
+      <c r="H1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L1" t="s">
+        <v>146</v>
+      </c>
+      <c r="M1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N1" t="s">
+        <v>148</v>
+      </c>
+      <c r="O1" t="s">
+        <v>149</v>
+      </c>
+      <c r="P1" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>151</v>
+      </c>
+      <c r="R1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S1" t="s">
+        <v>24</v>
+      </c>
+      <c r="T1" t="s">
+        <v>25</v>
+      </c>
+      <c r="U1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21">
+      <c r="A2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>3000001276</v>
+      </c>
+      <c r="D2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I2">
+        <v>2.16</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1.01604</v>
+      </c>
+      <c r="L2" s="1">
+        <v>45638</v>
+      </c>
+      <c r="M2" t="s">
+        <v>155</v>
+      </c>
+      <c r="N2" t="s">
+        <v>156</v>
+      </c>
+      <c r="O2">
+        <v>3</v>
+      </c>
+      <c r="P2" t="s">
+        <v>157</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21">
+      <c r="A3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3">
+        <v>3000001276</v>
+      </c>
+      <c r="D3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" t="s">
+        <v>159</v>
+      </c>
+      <c r="H3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I3">
+        <v>-0.32</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>1.01604</v>
+      </c>
+      <c r="L3" s="1">
+        <v>45638</v>
+      </c>
+      <c r="M3" t="s">
+        <v>155</v>
+      </c>
+      <c r="N3" t="s">
+        <v>156</v>
+      </c>
+      <c r="O3">
+        <v>3</v>
+      </c>
+      <c r="P3" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q3">
+        <v>15</v>
+      </c>
+      <c r="R3" t="s">
+        <v>38</v>
+      </c>
+      <c r="S3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T3" t="s">
+        <v>40</v>
+      </c>
+      <c r="U3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4">
+        <v>3000001265</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" t="s">
+        <v>47</v>
+      </c>
+      <c r="H4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I4">
+        <v>-5.63</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4" s="1">
+        <v>45628</v>
+      </c>
+      <c r="M4" t="s">
+        <v>161</v>
+      </c>
+      <c r="N4" t="s">
+        <v>161</v>
+      </c>
+      <c r="P4" t="s">
+        <v>161</v>
+      </c>
+      <c r="U4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5">
+        <v>3000001254</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" t="s">
+        <v>47</v>
+      </c>
+      <c r="H5" t="s">
+        <v>162</v>
+      </c>
+      <c r="I5">
+        <v>-4.68</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5" s="1">
+        <v>45597</v>
+      </c>
+      <c r="M5" t="s">
+        <v>161</v>
+      </c>
+      <c r="N5" t="s">
+        <v>161</v>
+      </c>
+      <c r="P5" t="s">
+        <v>161</v>
+      </c>
+      <c r="U5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6">
+        <v>3000001243</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H6" t="s">
+        <v>162</v>
+      </c>
+      <c r="I6">
+        <v>-4.54</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1">
+        <v>45566</v>
+      </c>
+      <c r="M6" t="s">
+        <v>161</v>
+      </c>
+      <c r="N6" t="s">
+        <v>161</v>
+      </c>
+      <c r="P6" t="s">
+        <v>161</v>
+      </c>
+      <c r="U6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7">
+        <v>3000001232</v>
+      </c>
+      <c r="D7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" t="s">
+        <v>153</v>
+      </c>
+      <c r="H7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I7">
+        <v>9</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0.734815</v>
+      </c>
+      <c r="L7" s="1">
+        <v>45566</v>
+      </c>
+      <c r="M7" t="s">
+        <v>164</v>
+      </c>
+      <c r="N7" t="s">
+        <v>161</v>
+      </c>
+      <c r="O7">
+        <v>199</v>
+      </c>
+      <c r="P7" t="s">
+        <v>165</v>
+      </c>
+      <c r="R7" t="s">
+        <v>57</v>
+      </c>
+      <c r="S7" t="s">
+        <v>58</v>
+      </c>
+      <c r="T7" t="s">
+        <v>59</v>
+      </c>
+      <c r="U7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8">
+        <v>3000001232</v>
+      </c>
+      <c r="D8" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F8" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>159</v>
+      </c>
+      <c r="H8" t="s">
+        <v>160</v>
+      </c>
+      <c r="I8">
+        <v>-3</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0.734815</v>
+      </c>
+      <c r="L8" s="1">
+        <v>45566</v>
+      </c>
+      <c r="M8" t="s">
+        <v>164</v>
+      </c>
+      <c r="N8" t="s">
+        <v>161</v>
+      </c>
+      <c r="O8">
+        <v>199</v>
+      </c>
+      <c r="P8" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q8">
+        <v>25</v>
+      </c>
+      <c r="R8" t="s">
+        <v>57</v>
+      </c>
+      <c r="S8" t="s">
+        <v>58</v>
+      </c>
+      <c r="T8" t="s">
+        <v>59</v>
+      </c>
+      <c r="U8" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9">
+        <v>3000001221</v>
+      </c>
+      <c r="D9" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" t="s">
+        <v>160</v>
+      </c>
+      <c r="I9">
+        <v>-0.3</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0.98295</v>
+      </c>
+      <c r="L9" s="1">
+        <v>45547</v>
+      </c>
+      <c r="M9" t="s">
+        <v>168</v>
+      </c>
+      <c r="N9" t="s">
+        <v>169</v>
+      </c>
+      <c r="O9">
+        <v>3</v>
+      </c>
+      <c r="P9" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q9">
+        <v>15</v>
+      </c>
+      <c r="R9" t="s">
+        <v>38</v>
+      </c>
+      <c r="S9" t="s">
+        <v>39</v>
+      </c>
+      <c r="T9" t="s">
+        <v>40</v>
+      </c>
+      <c r="U9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>3000001221</v>
+      </c>
+      <c r="D10" t="s">
+        <v>170</v>
+      </c>
+      <c r="E10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" t="s">
+        <v>153</v>
+      </c>
+      <c r="H10" t="s">
+        <v>154</v>
+      </c>
+      <c r="I10">
+        <v>1.95</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.98295</v>
+      </c>
+      <c r="L10" s="1">
+        <v>45547</v>
+      </c>
+      <c r="M10" t="s">
+        <v>168</v>
+      </c>
+      <c r="N10" t="s">
+        <v>169</v>
+      </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
+      <c r="P10" t="s">
+        <v>171</v>
+      </c>
+      <c r="R10" t="s">
+        <v>38</v>
+      </c>
+      <c r="S10" t="s">
+        <v>39</v>
+      </c>
+      <c r="T10" t="s">
+        <v>40</v>
+      </c>
+      <c r="U10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11">
+        <v>3000001210</v>
+      </c>
+      <c r="D11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" t="s">
+        <v>162</v>
+      </c>
+      <c r="I11">
+        <v>-4.65</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" s="1">
+        <v>45537</v>
+      </c>
+      <c r="M11" t="s">
+        <v>161</v>
+      </c>
+      <c r="N11" t="s">
+        <v>161</v>
+      </c>
+      <c r="P11" t="s">
+        <v>161</v>
+      </c>
+      <c r="U11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12">
+        <v>3000001199</v>
+      </c>
+      <c r="D12" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G12" t="s">
+        <v>173</v>
+      </c>
+      <c r="H12" t="s">
+        <v>174</v>
+      </c>
+      <c r="I12">
+        <v>0.94</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>1</v>
+      </c>
+      <c r="L12" s="1">
+        <v>45516</v>
+      </c>
+      <c r="M12" t="s">
+        <v>175</v>
+      </c>
+      <c r="N12" t="s">
+        <v>176</v>
+      </c>
+      <c r="O12">
+        <v>3</v>
+      </c>
+      <c r="P12" t="s">
+        <v>161</v>
+      </c>
+      <c r="R12" t="s">
+        <v>66</v>
+      </c>
+      <c r="S12" t="s">
+        <v>67</v>
+      </c>
+      <c r="T12" t="s">
+        <v>68</v>
+      </c>
+      <c r="U12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13">
+        <v>3000001199</v>
+      </c>
+      <c r="D13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" t="s">
+        <v>159</v>
+      </c>
+      <c r="H13" t="s">
+        <v>160</v>
+      </c>
+      <c r="I13">
+        <v>-0.14</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1">
+        <v>45516</v>
+      </c>
+      <c r="M13" t="s">
+        <v>175</v>
+      </c>
+      <c r="N13" t="s">
+        <v>176</v>
+      </c>
+      <c r="O13">
+        <v>3</v>
+      </c>
+      <c r="P13" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q13">
+        <v>15</v>
+      </c>
+      <c r="R13" t="s">
+        <v>66</v>
+      </c>
+      <c r="S13" t="s">
+        <v>67</v>
+      </c>
+      <c r="T13" t="s">
+        <v>68</v>
+      </c>
+      <c r="U13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14">
+        <v>3000001188</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G14" t="s">
+        <v>71</v>
+      </c>
+      <c r="H14" t="s">
+        <v>178</v>
+      </c>
+      <c r="I14">
+        <v>0.53</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14" s="1">
+        <v>45509</v>
+      </c>
+      <c r="M14" t="s">
+        <v>161</v>
+      </c>
+      <c r="N14" t="s">
+        <v>161</v>
+      </c>
+      <c r="P14" t="s">
+        <v>161</v>
+      </c>
+      <c r="U14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15">
+        <v>3000001177</v>
+      </c>
+      <c r="D15" t="s">
+        <v>179</v>
+      </c>
+      <c r="E15" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" t="s">
+        <v>65</v>
+      </c>
+      <c r="G15" t="s">
+        <v>173</v>
+      </c>
+      <c r="H15" t="s">
+        <v>174</v>
+      </c>
+      <c r="I15">
+        <v>0.22</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15" s="1">
+        <v>45505</v>
+      </c>
+      <c r="M15" t="s">
+        <v>180</v>
+      </c>
+      <c r="N15" t="s">
+        <v>181</v>
+      </c>
+      <c r="O15">
+        <v>3</v>
+      </c>
+      <c r="P15" t="s">
+        <v>161</v>
+      </c>
+      <c r="R15" t="s">
+        <v>74</v>
+      </c>
+      <c r="S15" t="s">
+        <v>75</v>
+      </c>
+      <c r="T15" t="s">
+        <v>76</v>
+      </c>
+      <c r="U15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C16">
+        <v>3000001177</v>
+      </c>
+      <c r="D16" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G16" t="s">
+        <v>159</v>
+      </c>
+      <c r="H16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I16">
+        <v>-0.04</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16" s="1">
+        <v>45505</v>
+      </c>
+      <c r="M16" t="s">
+        <v>180</v>
+      </c>
+      <c r="N16" t="s">
+        <v>181</v>
+      </c>
+      <c r="O16">
+        <v>3</v>
+      </c>
+      <c r="P16" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q16">
+        <v>15</v>
+      </c>
+      <c r="R16" t="s">
+        <v>74</v>
+      </c>
+      <c r="S16" t="s">
+        <v>75</v>
+      </c>
+      <c r="T16" t="s">
+        <v>76</v>
+      </c>
+      <c r="U16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17">
+        <v>3000001166</v>
+      </c>
+      <c r="D17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
+        <v>47</v>
+      </c>
+      <c r="G17" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" t="s">
+        <v>162</v>
+      </c>
+      <c r="I17">
+        <v>-4.31</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1">
+        <v>45505</v>
+      </c>
+      <c r="M17" t="s">
+        <v>161</v>
+      </c>
+      <c r="N17" t="s">
+        <v>161</v>
+      </c>
+      <c r="P17" t="s">
+        <v>161</v>
+      </c>
+      <c r="U17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18">
+        <v>3000001155</v>
+      </c>
+      <c r="D18" t="s">
+        <v>79</v>
+      </c>
+      <c r="F18" t="s">
+        <v>47</v>
+      </c>
+      <c r="G18" t="s">
+        <v>47</v>
+      </c>
+      <c r="H18" t="s">
+        <v>162</v>
+      </c>
+      <c r="I18">
+        <v>-1.6</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
+      </c>
+      <c r="L18" s="1">
+        <v>45495</v>
+      </c>
+      <c r="M18" t="s">
+        <v>161</v>
+      </c>
+      <c r="N18" t="s">
+        <v>161</v>
+      </c>
+      <c r="P18" t="s">
+        <v>161</v>
+      </c>
+      <c r="U18" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19">
+        <v>3000001144</v>
+      </c>
+      <c r="D19" t="s">
+        <v>183</v>
+      </c>
+      <c r="E19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" t="s">
+        <v>159</v>
+      </c>
+      <c r="H19" t="s">
+        <v>160</v>
+      </c>
+      <c r="I19">
+        <v>-2.05</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0.73923</v>
+      </c>
+      <c r="L19" s="1">
+        <v>45475</v>
+      </c>
+      <c r="M19" t="s">
+        <v>184</v>
+      </c>
+      <c r="N19" t="s">
+        <v>185</v>
+      </c>
+      <c r="O19">
+        <v>199</v>
+      </c>
+      <c r="P19" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q19">
+        <v>25</v>
+      </c>
+      <c r="R19" t="s">
+        <v>57</v>
+      </c>
+      <c r="S19" t="s">
+        <v>58</v>
+      </c>
+      <c r="T19" t="s">
+        <v>59</v>
+      </c>
+      <c r="U19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20">
+        <v>3000001144</v>
+      </c>
+      <c r="D20" t="s">
+        <v>186</v>
+      </c>
+      <c r="E20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" t="s">
+        <v>153</v>
+      </c>
+      <c r="H20" t="s">
+        <v>154</v>
+      </c>
+      <c r="I20">
+        <v>8.13</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0.73923</v>
+      </c>
+      <c r="L20" s="1">
+        <v>45475</v>
+      </c>
+      <c r="M20" t="s">
+        <v>184</v>
+      </c>
+      <c r="N20" t="s">
+        <v>185</v>
+      </c>
+      <c r="O20">
+        <v>199</v>
+      </c>
+      <c r="P20" t="s">
+        <v>165</v>
+      </c>
+      <c r="R20" t="s">
+        <v>57</v>
+      </c>
+      <c r="S20" t="s">
+        <v>58</v>
+      </c>
+      <c r="T20" t="s">
+        <v>59</v>
+      </c>
+      <c r="U20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21">
+        <v>3000001133</v>
+      </c>
+      <c r="D21" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" t="s">
+        <v>47</v>
+      </c>
+      <c r="G21" t="s">
+        <v>47</v>
+      </c>
+      <c r="H21" t="s">
+        <v>162</v>
+      </c>
+      <c r="I21">
+        <v>-4.71</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>1</v>
+      </c>
+      <c r="L21" s="1">
+        <v>45474</v>
+      </c>
+      <c r="M21" t="s">
+        <v>161</v>
+      </c>
+      <c r="N21" t="s">
+        <v>161</v>
+      </c>
+      <c r="P21" t="s">
+        <v>161</v>
+      </c>
+      <c r="U21" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22">
+        <v>3000001122</v>
+      </c>
+      <c r="D22" t="s">
+        <v>187</v>
+      </c>
+      <c r="E22" t="s">
+        <v>84</v>
+      </c>
+      <c r="F22" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" t="s">
+        <v>153</v>
+      </c>
+      <c r="H22" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22">
+        <v>2.28</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>0.894286</v>
+      </c>
+      <c r="L22" s="1">
+        <v>45456</v>
+      </c>
+      <c r="M22" t="s">
+        <v>188</v>
+      </c>
+      <c r="N22" t="s">
+        <v>189</v>
+      </c>
+      <c r="O22">
+        <v>3</v>
+      </c>
+      <c r="P22" t="s">
+        <v>171</v>
+      </c>
+      <c r="R22" t="s">
+        <v>38</v>
+      </c>
+      <c r="S22" t="s">
+        <v>39</v>
+      </c>
+      <c r="T22" t="s">
+        <v>40</v>
+      </c>
+      <c r="U22" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23">
+        <v>3000001122</v>
+      </c>
+      <c r="D23" t="s">
+        <v>190</v>
+      </c>
+      <c r="E23" t="s">
+        <v>84</v>
+      </c>
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" t="s">
+        <v>160</v>
+      </c>
+      <c r="I23">
+        <v>-0.35</v>
+      </c>
+      <c r="J23">
+        <v>0</v>
+      </c>
+      <c r="K23">
+        <v>0.894286</v>
+      </c>
+      <c r="L23" s="1">
+        <v>45456</v>
+      </c>
+      <c r="M23" t="s">
+        <v>188</v>
+      </c>
+      <c r="N23" t="s">
+        <v>189</v>
+      </c>
+      <c r="O23">
+        <v>3</v>
+      </c>
+      <c r="P23" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q23">
+        <v>15</v>
+      </c>
+      <c r="R23" t="s">
+        <v>38</v>
+      </c>
+      <c r="S23" t="s">
+        <v>39</v>
+      </c>
+      <c r="T23" t="s">
+        <v>40</v>
+      </c>
+      <c r="U23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C24">
+        <v>3000001111</v>
+      </c>
+      <c r="D24" t="s">
+        <v>191</v>
+      </c>
+      <c r="E24" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" t="s">
+        <v>35</v>
+      </c>
+      <c r="G24" t="s">
+        <v>159</v>
+      </c>
+      <c r="H24" t="s">
+        <v>160</v>
+      </c>
+      <c r="I24">
+        <v>-1.3</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>1</v>
+      </c>
+      <c r="L24" s="1">
+        <v>45450</v>
+      </c>
+      <c r="M24" t="s">
+        <v>192</v>
+      </c>
+      <c r="N24" t="s">
+        <v>193</v>
+      </c>
+      <c r="O24">
+        <v>4</v>
+      </c>
+      <c r="P24" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q24">
+        <v>15</v>
+      </c>
+      <c r="R24" t="s">
+        <v>86</v>
+      </c>
+      <c r="S24" t="s">
+        <v>87</v>
+      </c>
+      <c r="T24" t="s">
+        <v>88</v>
+      </c>
+      <c r="U24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25">
+        <v>3000001111</v>
+      </c>
+      <c r="D25" t="s">
+        <v>194</v>
+      </c>
+      <c r="E25" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" t="s">
+        <v>35</v>
+      </c>
+      <c r="G25" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" t="s">
+        <v>154</v>
+      </c>
+      <c r="I25">
+        <v>8.2</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25" s="1">
+        <v>45450</v>
+      </c>
+      <c r="M25" t="s">
+        <v>192</v>
+      </c>
+      <c r="N25" t="s">
+        <v>193</v>
+      </c>
+      <c r="O25">
+        <v>4</v>
+      </c>
+      <c r="P25" t="s">
+        <v>195</v>
+      </c>
+      <c r="R25" t="s">
+        <v>86</v>
+      </c>
+      <c r="S25" t="s">
+        <v>87</v>
+      </c>
+      <c r="T25" t="s">
+        <v>88</v>
+      </c>
+      <c r="U25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C26">
+        <v>3000001100</v>
+      </c>
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="F26" t="s">
+        <v>47</v>
+      </c>
+      <c r="G26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" t="s">
+        <v>162</v>
+      </c>
+      <c r="I26">
+        <v>-2.4</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>1</v>
+      </c>
+      <c r="L26" s="1">
+        <v>45446</v>
+      </c>
+      <c r="M26" t="s">
+        <v>161</v>
+      </c>
+      <c r="N26" t="s">
+        <v>161</v>
+      </c>
+      <c r="P26" t="s">
+        <v>161</v>
+      </c>
+      <c r="U26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" t="s">
+        <v>44</v>
+      </c>
+      <c r="C27">
+        <v>3000001089</v>
+      </c>
+      <c r="D27" t="s">
+        <v>196</v>
+      </c>
+      <c r="E27" t="s">
+        <v>92</v>
+      </c>
+      <c r="F27" t="s">
+        <v>35</v>
+      </c>
+      <c r="G27" t="s">
+        <v>173</v>
+      </c>
+      <c r="H27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I27">
+        <v>2.37</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27" s="1">
+        <v>45436</v>
+      </c>
+      <c r="M27" t="s">
+        <v>197</v>
+      </c>
+      <c r="N27" t="s">
+        <v>176</v>
+      </c>
+      <c r="P27" t="s">
+        <v>161</v>
+      </c>
+      <c r="R27" t="s">
+        <v>93</v>
+      </c>
+      <c r="S27" t="s">
+        <v>94</v>
+      </c>
+      <c r="T27" t="s">
+        <v>95</v>
+      </c>
+      <c r="U27" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="C28">
+        <v>3000001078</v>
+      </c>
+      <c r="D28" t="s">
+        <v>198</v>
+      </c>
+      <c r="E28" t="s">
+        <v>97</v>
+      </c>
+      <c r="F28" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" t="s">
+        <v>173</v>
+      </c>
+      <c r="H28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I28">
+        <v>2.49</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28" s="1">
+        <v>45415</v>
+      </c>
+      <c r="M28" t="s">
+        <v>199</v>
+      </c>
+      <c r="N28" t="s">
+        <v>200</v>
+      </c>
+      <c r="O28">
+        <v>3</v>
+      </c>
+      <c r="P28" t="s">
+        <v>161</v>
+      </c>
+      <c r="R28" t="s">
+        <v>66</v>
+      </c>
+      <c r="S28" t="s">
+        <v>67</v>
+      </c>
+      <c r="T28" t="s">
+        <v>68</v>
+      </c>
+      <c r="U28" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21">
+      <c r="A29" t="s">
+        <v>44</v>
+      </c>
+      <c r="C29">
+        <v>3000001078</v>
+      </c>
+      <c r="D29" t="s">
+        <v>201</v>
+      </c>
+      <c r="E29" t="s">
+        <v>97</v>
+      </c>
+      <c r="F29" t="s">
+        <v>65</v>
+      </c>
+      <c r="G29" t="s">
+        <v>159</v>
+      </c>
+      <c r="H29" t="s">
+        <v>160</v>
+      </c>
+      <c r="I29">
+        <v>-0.37</v>
+      </c>
+      <c r="J29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29" s="1">
+        <v>45415</v>
+      </c>
+      <c r="M29" t="s">
+        <v>199</v>
+      </c>
+      <c r="N29" t="s">
+        <v>200</v>
+      </c>
+      <c r="O29">
+        <v>3</v>
+      </c>
+      <c r="P29" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q29">
+        <v>15</v>
+      </c>
+      <c r="R29" t="s">
+        <v>66</v>
+      </c>
+      <c r="S29" t="s">
+        <v>67</v>
+      </c>
+      <c r="T29" t="s">
+        <v>68</v>
+      </c>
+      <c r="U29" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21">
+      <c r="A30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30">
+        <v>3000001067</v>
+      </c>
+      <c r="D30" t="s">
+        <v>98</v>
+      </c>
+      <c r="F30" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" t="s">
+        <v>162</v>
+      </c>
+      <c r="I30">
+        <v>-8.22</v>
+      </c>
+      <c r="J30">
+        <v>0</v>
+      </c>
+      <c r="K30">
+        <v>1</v>
+      </c>
+      <c r="L30" s="1">
+        <v>45413</v>
+      </c>
+      <c r="M30" t="s">
+        <v>161</v>
+      </c>
+      <c r="N30" t="s">
+        <v>161</v>
+      </c>
+      <c r="P30" t="s">
+        <v>161</v>
+      </c>
+      <c r="U30" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21">
+      <c r="A31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31">
+        <v>3000001056</v>
+      </c>
+      <c r="D31" t="s">
+        <v>100</v>
+      </c>
+      <c r="F31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G31" t="s">
+        <v>71</v>
+      </c>
+      <c r="H31" t="s">
+        <v>178</v>
+      </c>
+      <c r="I31">
+        <v>1.43</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1">
+        <v>45413</v>
+      </c>
+      <c r="M31" t="s">
+        <v>161</v>
+      </c>
+      <c r="N31" t="s">
+        <v>161</v>
+      </c>
+      <c r="P31" t="s">
+        <v>161</v>
+      </c>
+      <c r="U31" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21">
+      <c r="A32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32">
+        <v>3000001045</v>
+      </c>
+      <c r="D32" t="s">
+        <v>202</v>
+      </c>
+      <c r="E32" t="s">
+        <v>102</v>
+      </c>
+      <c r="F32" t="s">
+        <v>65</v>
+      </c>
+      <c r="G32" t="s">
+        <v>159</v>
+      </c>
+      <c r="H32" t="s">
+        <v>160</v>
+      </c>
+      <c r="I32">
+        <v>-0.05</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1">
+        <v>45407</v>
+      </c>
+      <c r="M32" t="s">
+        <v>203</v>
+      </c>
+      <c r="N32" t="s">
+        <v>204</v>
+      </c>
+      <c r="O32">
+        <v>3</v>
+      </c>
+      <c r="P32" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q32">
+        <v>15</v>
+      </c>
+      <c r="R32" t="s">
+        <v>74</v>
+      </c>
+      <c r="S32" t="s">
+        <v>75</v>
+      </c>
+      <c r="T32" t="s">
+        <v>76</v>
+      </c>
+      <c r="U32" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33">
+        <v>3000001045</v>
+      </c>
+      <c r="D33" t="s">
+        <v>205</v>
+      </c>
+      <c r="E33" t="s">
+        <v>102</v>
+      </c>
+      <c r="F33" t="s">
+        <v>65</v>
+      </c>
+      <c r="G33" t="s">
+        <v>173</v>
+      </c>
+      <c r="H33" t="s">
+        <v>174</v>
+      </c>
+      <c r="I33">
+        <v>0.32</v>
+      </c>
+      <c r="J33">
+        <v>0</v>
+      </c>
+      <c r="K33">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1">
+        <v>45407</v>
+      </c>
+      <c r="M33" t="s">
+        <v>203</v>
+      </c>
+      <c r="N33" t="s">
+        <v>204</v>
+      </c>
+      <c r="O33">
+        <v>3</v>
+      </c>
+      <c r="P33" t="s">
+        <v>161</v>
+      </c>
+      <c r="R33" t="s">
+        <v>74</v>
+      </c>
+      <c r="S33" t="s">
+        <v>75</v>
+      </c>
+      <c r="T33" t="s">
+        <v>76</v>
+      </c>
+      <c r="U33" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21">
+      <c r="A34" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34">
+        <v>3000001034</v>
+      </c>
+      <c r="D34" t="s">
+        <v>103</v>
+      </c>
+      <c r="F34" t="s">
+        <v>104</v>
+      </c>
+      <c r="G34" t="s">
+        <v>104</v>
+      </c>
+      <c r="H34" t="s">
+        <v>206</v>
+      </c>
+      <c r="I34">
+        <v>-0.74</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0.940525</v>
+      </c>
+      <c r="L34" s="1">
+        <v>45407</v>
+      </c>
+      <c r="M34" t="s">
+        <v>161</v>
+      </c>
+      <c r="N34" t="s">
+        <v>161</v>
+      </c>
+      <c r="P34" t="s">
+        <v>161</v>
+      </c>
+      <c r="R34" t="s">
+        <v>106</v>
+      </c>
+      <c r="S34" t="s">
+        <v>107</v>
+      </c>
+      <c r="T34" t="s">
+        <v>108</v>
+      </c>
+      <c r="U34" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21">
+      <c r="A35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35">
+        <v>3000001023</v>
+      </c>
+      <c r="D35" t="s">
+        <v>110</v>
+      </c>
+      <c r="F35" t="s">
+        <v>47</v>
+      </c>
+      <c r="G35" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" t="s">
+        <v>162</v>
+      </c>
+      <c r="I35">
+        <v>-8.08</v>
+      </c>
+      <c r="J35">
+        <v>0</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1">
+        <v>45383</v>
+      </c>
+      <c r="M35" t="s">
+        <v>161</v>
+      </c>
+      <c r="N35" t="s">
+        <v>161</v>
+      </c>
+      <c r="P35" t="s">
+        <v>161</v>
+      </c>
+      <c r="U35" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21">
+      <c r="A36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C36">
+        <v>3000001012</v>
+      </c>
+      <c r="D36" t="s">
+        <v>112</v>
+      </c>
+      <c r="F36" t="s">
+        <v>71</v>
+      </c>
+      <c r="G36" t="s">
+        <v>71</v>
+      </c>
+      <c r="H36" t="s">
+        <v>178</v>
+      </c>
+      <c r="I36">
+        <v>1.4</v>
+      </c>
+      <c r="J36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1">
+        <v>45383</v>
+      </c>
+      <c r="M36" t="s">
+        <v>161</v>
+      </c>
+      <c r="N36" t="s">
+        <v>161</v>
+      </c>
+      <c r="P36" t="s">
+        <v>161</v>
+      </c>
+      <c r="U36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21">
+      <c r="A37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37">
+        <v>3000001001</v>
+      </c>
+      <c r="D37" t="s">
+        <v>207</v>
+      </c>
+      <c r="E37" t="s">
+        <v>114</v>
+      </c>
+      <c r="F37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G37" t="s">
+        <v>159</v>
+      </c>
+      <c r="H37" t="s">
+        <v>160</v>
+      </c>
+      <c r="I37">
+        <v>-2.22</v>
+      </c>
+      <c r="J37">
+        <v>0</v>
+      </c>
+      <c r="K37">
+        <v>0.700936</v>
+      </c>
+      <c r="L37" s="1">
+        <v>45383</v>
+      </c>
+      <c r="M37" t="s">
+        <v>208</v>
+      </c>
+      <c r="N37" t="s">
+        <v>209</v>
+      </c>
+      <c r="O37">
+        <v>199</v>
+      </c>
+      <c r="P37" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q37">
+        <v>25</v>
+      </c>
+      <c r="R37" t="s">
+        <v>57</v>
+      </c>
+      <c r="S37" t="s">
+        <v>58</v>
+      </c>
+      <c r="T37" t="s">
+        <v>59</v>
+      </c>
+      <c r="U37" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C38">
+        <v>3000001001</v>
+      </c>
+      <c r="D38" t="s">
+        <v>210</v>
+      </c>
+      <c r="E38" t="s">
+        <v>114</v>
+      </c>
+      <c r="F38" t="s">
+        <v>35</v>
+      </c>
+      <c r="G38" t="s">
+        <v>153</v>
+      </c>
+      <c r="H38" t="s">
+        <v>154</v>
+      </c>
+      <c r="I38">
+        <v>8.88</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>0.700936</v>
+      </c>
+      <c r="L38" s="1">
+        <v>45383</v>
+      </c>
+      <c r="M38" t="s">
+        <v>208</v>
+      </c>
+      <c r="N38" t="s">
+        <v>209</v>
+      </c>
+      <c r="O38">
+        <v>199</v>
+      </c>
+      <c r="P38" t="s">
+        <v>165</v>
+      </c>
+      <c r="R38" t="s">
+        <v>57</v>
+      </c>
+      <c r="S38" t="s">
+        <v>58</v>
+      </c>
+      <c r="T38" t="s">
+        <v>59</v>
+      </c>
+      <c r="U38" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21">
+      <c r="A39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39">
+        <v>3000000990</v>
+      </c>
+      <c r="D39" t="s">
+        <v>211</v>
+      </c>
+      <c r="E39" t="s">
+        <v>115</v>
+      </c>
+      <c r="F39" t="s">
+        <v>35</v>
+      </c>
+      <c r="G39" t="s">
+        <v>159</v>
+      </c>
+      <c r="H39" t="s">
+        <v>160</v>
+      </c>
+      <c r="I39">
+        <v>-0.34</v>
+      </c>
+      <c r="J39">
+        <v>0</v>
+      </c>
+      <c r="K39">
+        <v>0.971562</v>
+      </c>
+      <c r="L39" s="1">
+        <v>45365</v>
+      </c>
+      <c r="M39" t="s">
+        <v>212</v>
+      </c>
+      <c r="N39" t="s">
+        <v>213</v>
+      </c>
+      <c r="O39">
+        <v>3</v>
+      </c>
+      <c r="P39" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q39">
+        <v>15</v>
+      </c>
+      <c r="R39" t="s">
+        <v>38</v>
+      </c>
+      <c r="S39" t="s">
+        <v>39</v>
+      </c>
+      <c r="T39" t="s">
+        <v>40</v>
+      </c>
+      <c r="U39" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21">
+      <c r="A40" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40">
+        <v>3000000990</v>
+      </c>
+      <c r="D40" t="s">
+        <v>214</v>
+      </c>
+      <c r="E40" t="s">
+        <v>115</v>
+      </c>
+      <c r="F40" t="s">
+        <v>35</v>
+      </c>
+      <c r="G40" t="s">
+        <v>153</v>
+      </c>
+      <c r="H40" t="s">
+        <v>154</v>
+      </c>
+      <c r="I40">
+        <v>2.05</v>
+      </c>
+      <c r="J40">
+        <v>0</v>
+      </c>
+      <c r="K40">
+        <v>0.971562</v>
+      </c>
+      <c r="L40" s="1">
+        <v>45365</v>
+      </c>
+      <c r="M40" t="s">
+        <v>212</v>
+      </c>
+      <c r="N40" t="s">
+        <v>213</v>
+      </c>
+      <c r="O40">
+        <v>3</v>
+      </c>
+      <c r="P40" t="s">
+        <v>171</v>
+      </c>
+      <c r="R40" t="s">
+        <v>38</v>
+      </c>
+      <c r="S40" t="s">
+        <v>39</v>
+      </c>
+      <c r="T40" t="s">
+        <v>40</v>
+      </c>
+      <c r="U40" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41">
+        <v>3000000979</v>
+      </c>
+      <c r="D41" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" t="s">
+        <v>71</v>
+      </c>
+      <c r="G41" t="s">
+        <v>71</v>
+      </c>
+      <c r="H41" t="s">
+        <v>178</v>
+      </c>
+      <c r="I41">
+        <v>1.43</v>
+      </c>
+      <c r="J41">
+        <v>0</v>
+      </c>
+      <c r="K41">
+        <v>1</v>
+      </c>
+      <c r="L41" s="1">
+        <v>45352</v>
+      </c>
+      <c r="M41" t="s">
+        <v>161</v>
+      </c>
+      <c r="N41" t="s">
+        <v>161</v>
+      </c>
+      <c r="P41" t="s">
+        <v>161</v>
+      </c>
+      <c r="U41" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42">
+        <v>3000000968</v>
+      </c>
+      <c r="D42" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" t="s">
+        <v>47</v>
+      </c>
+      <c r="G42" t="s">
+        <v>47</v>
+      </c>
+      <c r="H42" t="s">
+        <v>162</v>
+      </c>
+      <c r="I42">
+        <v>-7.79</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42" s="1">
+        <v>45352</v>
+      </c>
+      <c r="M42" t="s">
+        <v>161</v>
+      </c>
+      <c r="N42" t="s">
+        <v>161</v>
+      </c>
+      <c r="P42" t="s">
+        <v>161</v>
+      </c>
+      <c r="U42" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43">
+        <v>3000000957</v>
+      </c>
+      <c r="D43" t="s">
+        <v>120</v>
+      </c>
+      <c r="F43" t="s">
+        <v>71</v>
+      </c>
+      <c r="G43" t="s">
+        <v>71</v>
+      </c>
+      <c r="H43" t="s">
+        <v>178</v>
+      </c>
+      <c r="I43">
+        <v>1.53</v>
+      </c>
+      <c r="J43">
+        <v>0</v>
+      </c>
+      <c r="K43">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1">
+        <v>45323</v>
+      </c>
+      <c r="M43" t="s">
+        <v>161</v>
+      </c>
+      <c r="N43" t="s">
+        <v>161</v>
+      </c>
+      <c r="P43" t="s">
+        <v>161</v>
+      </c>
+      <c r="U43" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="C44">
+        <v>3000000946</v>
+      </c>
+      <c r="D44" t="s">
+        <v>122</v>
+      </c>
+      <c r="F44" t="s">
+        <v>47</v>
+      </c>
+      <c r="G44" t="s">
+        <v>47</v>
+      </c>
+      <c r="H44" t="s">
+        <v>162</v>
+      </c>
+      <c r="I44">
+        <v>-8.24</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>1</v>
+      </c>
+      <c r="L44" s="1">
+        <v>45323</v>
+      </c>
+      <c r="M44" t="s">
+        <v>161</v>
+      </c>
+      <c r="N44" t="s">
+        <v>161</v>
+      </c>
+      <c r="P44" t="s">
+        <v>161</v>
+      </c>
+      <c r="U44" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="C45">
+        <v>3000000935</v>
+      </c>
+      <c r="D45" t="s">
+        <v>124</v>
+      </c>
+      <c r="F45" t="s">
+        <v>71</v>
+      </c>
+      <c r="G45" t="s">
+        <v>71</v>
+      </c>
+      <c r="H45" t="s">
+        <v>178</v>
+      </c>
+      <c r="I45">
+        <v>1.6</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45" s="1">
+        <v>45293</v>
+      </c>
+      <c r="M45" t="s">
+        <v>161</v>
+      </c>
+      <c r="N45" t="s">
+        <v>161</v>
+      </c>
+      <c r="P45" t="s">
+        <v>161</v>
+      </c>
+      <c r="U45" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21">
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="C46">
+        <v>3000000924</v>
+      </c>
+      <c r="D46" t="s">
+        <v>126</v>
+      </c>
+      <c r="F46" t="s">
+        <v>47</v>
+      </c>
+      <c r="G46" t="s">
+        <v>47</v>
+      </c>
+      <c r="H46" t="s">
+        <v>162</v>
+      </c>
+      <c r="I46">
+        <v>-8.2</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>1</v>
+      </c>
+      <c r="L46" s="1">
+        <v>45293</v>
+      </c>
+      <c r="M46" t="s">
+        <v>161</v>
+      </c>
+      <c r="N46" t="s">
+        <v>161</v>
+      </c>
+      <c r="P46" t="s">
+        <v>161</v>
+      </c>
+      <c r="U46" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21">
+      <c r="A47" t="s">
+        <v>54</v>
+      </c>
+      <c r="C47">
+        <v>3000000913</v>
+      </c>
+      <c r="D47" t="s">
+        <v>215</v>
+      </c>
+      <c r="E47" t="s">
+        <v>128</v>
+      </c>
+      <c r="F47" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" t="s">
+        <v>153</v>
+      </c>
+      <c r="H47" t="s">
+        <v>154</v>
+      </c>
+      <c r="I47">
+        <v>6.8</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0.729454</v>
+      </c>
+      <c r="L47" s="1">
+        <v>45293</v>
+      </c>
+      <c r="M47" t="s">
+        <v>213</v>
+      </c>
+      <c r="N47" t="s">
+        <v>216</v>
+      </c>
+      <c r="O47">
+        <v>199</v>
+      </c>
+      <c r="P47" t="s">
+        <v>165</v>
+      </c>
+      <c r="R47" t="s">
+        <v>57</v>
+      </c>
+      <c r="S47" t="s">
+        <v>58</v>
+      </c>
+      <c r="T47" t="s">
+        <v>59</v>
+      </c>
+      <c r="U47" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21">
+      <c r="A48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48">
+        <v>3000000913</v>
+      </c>
+      <c r="D48" t="s">
+        <v>217</v>
+      </c>
+      <c r="E48" t="s">
+        <v>128</v>
+      </c>
+      <c r="F48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G48" t="s">
+        <v>159</v>
+      </c>
+      <c r="H48" t="s">
+        <v>160</v>
+      </c>
+      <c r="I48">
+        <v>-1.7</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0.729454</v>
+      </c>
+      <c r="L48" s="1">
+        <v>45293</v>
+      </c>
+      <c r="M48" t="s">
+        <v>213</v>
+      </c>
+      <c r="N48" t="s">
+        <v>216</v>
+      </c>
+      <c r="O48">
+        <v>199</v>
+      </c>
+      <c r="P48" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q48">
+        <v>25</v>
+      </c>
+      <c r="R48" t="s">
+        <v>57</v>
+      </c>
+      <c r="S48" t="s">
+        <v>58</v>
+      </c>
+      <c r="T48" t="s">
+        <v>59</v>
+      </c>
+      <c r="U48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>